--- a/nursing/フォーマット/03_就労支援記録様式/06_個別支援計画書（就労継続支援版）.xlsx
+++ b/nursing/フォーマット/03_就労支援記録様式/06_個別支援計画書（就労継続支援版）.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="個別支援計画（就労支援版）" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="個別支援計画書" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -28,13 +28,20 @@
     <font>
       <name val="Meiryo UI"/>
       <b val="1"/>
-      <color rgb="000E7490"/>
+      <color rgb="FF0E7490"/>
       <sz val="13"/>
     </font>
     <font>
       <name val="Meiryo UI"/>
-      <color rgb="00DC2626"/>
+      <b val="1"/>
+      <color rgb="FFDC2626"/>
       <sz val="8"/>
+    </font>
+    <font>
+      <name val="Meiryo UI"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Meiryo UI"/>
@@ -47,15 +54,15 @@
     </font>
     <font>
       <name val="Meiryo UI"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <i val="1"/>
+      <color rgb="FF6B7280"/>
       <sz val="9"/>
     </font>
     <font>
       <name val="Meiryo UI"/>
-      <i val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="9"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="5">
@@ -67,17 +74,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFFAFE"/>
+        <fgColor rgb="FF0E7490"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000E7490"/>
+        <fgColor rgb="FFCFFAFE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8FAFC"/>
+        <fgColor rgb="FFF8FAFC"/>
       </patternFill>
     </fill>
   </fills>
@@ -99,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -108,15 +115,27 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -484,249 +503,721 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>個別支援計画書（就労継続支援A型・B型用）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
+          <t>個別支援計画書（就労継続支援A型・B型）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>※ 本様式は京都府版の補助様式です。公式様式（05_個別支援計画書様式（京都府）.docx）と併用してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="22" customHeight="1">
+          <t>【法令根拠】障害者総合支援法基準省令第58条・59条。サービス管理責任者が作成。利用者に説明し同意を得ること。6ヶ月ごとに見直し。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
+          <t>【基本情報】</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
           <t>利用者氏名</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>（様）</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>生年月日</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年　　月　　日（　　歳）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="22" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>（様）　　フリガナ：</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>生年月日・年齢</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　年　月　日生（　　歳）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>障害の種別・等級</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>身体(　級) ・ 精神(　級) ・ 知的(　) ・ 難病</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>身体(　級) / 精神(　級) / 知的(療育　) / 難病 / 複合</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>障害支援区分</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>区分　　　/認定日：　　年　　月</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>区分　　　　認定日：　　年　月</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>サービス種別</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>就労継続支援　A型 / B型</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>利用定員（施設）</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　名</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>計画作成日</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年　　月　　日</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　年　月　日</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>計画期間</t>
         </is>
       </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年　　月　〜　　年　　月</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>担当サービス管理責任者</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr"/>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>前回計画作成日</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　　年　　月　　日</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>【本人の希望・夢・目標】</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="50" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>（例）週4日、午後2時まで安定して作業できるようになりたい。将来的にパン屋でアルバイトしたい。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>【長期目標（6ヶ月〜1年）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="40" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>（例）毎日4時間の安定した就労ができる</t>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　年　月　日　〜　　年　月　日</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>計画の種別</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>新規 / 更新（前回作成日：　　年　月　日）</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>サービス管理責任者</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>前回のモニタリング実施日</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　　年　月　日</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>モニタリング頻度</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>6ヶ月ごと（状態変化時は随時）</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>【本人の意向・夢・将来への希望】（本人の言葉でそのまま記録する）</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>【短期目標（〜3ヶ月）】</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>（例）体調管理をして月間欠席2日以内を目指す</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>【具体的な支援内容】</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="80" customHeight="1">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>①日常的な体調確認と声かけ
-②休憩の取り方・体調悪化時の自己申告ができるよう支援
-③作業工程の分割・簡略化（本人の能力に合わせた調整）
-④一般就労への移行に向けた職場体験の機会を探る</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>【医療・保健との連携】</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="40" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>主治医：〇〇クリニック　田中医師　/ 訪問頻度：月1回以上の情報共有</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>【家族・居住環境との連携】</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="40" customHeight="1">
-      <c r="A18" s="6" t="inlineStr"/>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>【本人の同意】</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>上記の個別支援計画について説明を受け、内容に同意します。
-署名：　　　　　　　　　　　年　　月　　日</t>
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>例）「毎日通えるようになりたい」「給料をもらって自分で買い物したい」「いつか一般の仕事をしてみたい」</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>【家族・支援者の意向】</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>例）「無理せず続けてほしい」「体調の波があるので柔軟に対応してほしい」</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>【現状評価・アセスメント結果】</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="28" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>就労能力・作業能力</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>作業持続時間：　　h　作業の種類：　　　　　　集中力：高/中/低　指示理解：良好/困難</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="28" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>健康・体調管理</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>通院状況：　　　　服薬管理：自己/支援要　体調の波：大/小　精神状態：安定/不安定</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>対人関係・社会性</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>対人関係：良好/課題あり　　コミュニケーション：良好/困難</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="28" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>生活スキル・自立度</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>交通機関の利用：自立/支援要　金銭管理：自立/支援要　生活リズム：安定/不安定</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>障害の特性・配慮事項</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>例）大きな音に過敏。疲れると自傷行為が出る可能性あり。定期的な休憩が必要。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>【生活全般の解決すべき課題（ニーズ）と優先順位】</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>優先
+順位</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>課題（ニーズ）</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>本人・家族の意向</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>長期目標（6ヶ月〜1年）</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>短期目標（〜3ヶ月）</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>達成時期</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>評価指標</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>担当者</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="5" t="inlineStr"/>
+      <c r="B22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="inlineStr"/>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr"/>
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr"/>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+      <c r="E23" s="5" t="inlineStr"/>
+      <c r="F23" s="5" t="inlineStr"/>
+      <c r="G23" s="5" t="inlineStr"/>
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="5" t="inlineStr"/>
+      <c r="B24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="inlineStr"/>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr"/>
+      <c r="F24" s="5" t="inlineStr"/>
+      <c r="G24" s="5" t="inlineStr"/>
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="5" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr"/>
+      <c r="C25" s="5" t="inlineStr"/>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr"/>
+      <c r="F25" s="5" t="inlineStr"/>
+      <c r="G25" s="5" t="inlineStr"/>
+      <c r="H25" s="5" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>【提供するサービスの内容・量・担当者】（法令必須記載事項）</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>支援内容の種別</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>具体的な支援内容</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>頻度・時間</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>支援量（月）</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>担当者・職種</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>開始時期</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="inlineStr">
+        <is>
+          <t>終了時期</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>留意事項</t>
+        </is>
+      </c>
+      <c r="I27" s="7" t="inlineStr">
+        <is>
+          <t>特記</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="35" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>就労・作業支援</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>封入作業・箱折り・清掃作業の指導・支援</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>週4日・6時間/日</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>約96時間/月</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>職業指導員　田中</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>R7.4.1〜</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>計画期間末</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>疲れたら申告するよう促す</t>
+        </is>
+      </c>
+      <c r="I28" s="8" t="inlineStr"/>
+    </row>
+    <row r="29" ht="35" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>生活支援</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>毎日の健康チェック・服薬確認・昼食の準備補助</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="inlineStr">
+        <is>
+          <t>毎日</t>
+        </is>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>月20日</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>生活支援員　鈴木</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>R7.4.1〜</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>計画期間末</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>体調変化時は管理者へ報告</t>
+        </is>
+      </c>
+      <c r="I29" s="8" t="inlineStr"/>
+    </row>
+    <row r="30" ht="35" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>相談支援</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>週1回の個別面談・困りごとの相談</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="inlineStr">
+        <is>
+          <t>週1回30分</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>月4回</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>サービス管理責任者</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>R7.4.1〜</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>計画期間末</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="inlineStr"/>
+      <c r="I30" s="8" t="inlineStr"/>
+    </row>
+    <row r="31" ht="35" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>医療機関との連絡・連携</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>主治医との定期的な情報共有（月1回）</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="inlineStr">
+        <is>
+          <t>月1回</t>
+        </is>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>月1回</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>サービス管理責任者</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>R7.4.1〜</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>継続</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="inlineStr"/>
+      <c r="I31" s="8" t="inlineStr"/>
+    </row>
+    <row r="32" ht="32" customHeight="1">
+      <c r="A32" s="5" t="inlineStr"/>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr"/>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+    </row>
+    <row r="33" ht="32" customHeight="1">
+      <c r="A33" s="5" t="inlineStr"/>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr"/>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr"/>
+    </row>
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="5" t="inlineStr"/>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="5" t="inlineStr"/>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35" ht="32" customHeight="1">
+      <c r="A35" s="5" t="inlineStr"/>
+      <c r="B35" s="5" t="inlineStr"/>
+      <c r="C35" s="5" t="inlineStr"/>
+      <c r="D35" s="5" t="inlineStr"/>
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>【工賃目標・経済的自立（B型のみ・A型は賃金目標を記入）】</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="9" t="inlineStr">
+        <is>
+          <t>当月の目標工賃月額：　　　　円（前月実績：　　　　円）　一般就労移行の希望：あり / なし / 将来的に検討</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>【関係機関との連携内容】</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>主治医：　　　　　　（連携方法・頻度：　　　）　相談支援専門員：　　　　（連携方法：　　　）　家族：　　　（連携方法：　　　）</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>【本人・家族の同意欄】（法令必須）</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="80" customHeight="1">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>上記の個別支援計画について、サービス管理責任者より説明を受け、内容を確認し、同意しました。
+本人署名：　　　　　　　　　　　（　　年　月　日）　　保護者・代理人署名：　　　　　　　　続柄：　　　　（　　年　月　日）
+サービス管理責任者署名：　　　　　　　　　　（説明実施日：　　年　月　日）　　管理者確認：　　　　　　　　（　　年　月　日）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A1:H1"/>
+  <mergeCells count="50">
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="A41:I41"/>
+    <mergeCell ref="A37:I37"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="D17:I17"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="A3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="A12:I12"/>
+    <mergeCell ref="D16:I16"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="A14:I14"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D18:I18"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A20:I20"/>
+    <mergeCell ref="A38:I38"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="D15:I15"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A10:I10"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="A13:I13"/>
     <mergeCell ref="A5:B5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A40:I40"/>
+    <mergeCell ref="A39:I39"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="F9:G9"/>
+    <mergeCell ref="C6:E6"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="A20:H20"/>
-    <mergeCell ref="A10:H10"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A19:H19"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="D19:I19"/>
+    <mergeCell ref="A11:I11"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="A36:I36"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
